--- a/output/pdf_financials_xlsx/BLLG.xlsx
+++ b/output/pdf_financials_xlsx/BLLG.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/BLLG.xlsx
+++ b/output/pdf_financials_xlsx/BLLG.xlsx
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.507992</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.005385</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.027817</v>
       </c>
     </row>
     <row r="10">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.211792</v>
+        <v>0.719784</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-2.043642</v>
+        <v>2.043642</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-3.075485</v>
+        <v>3.075485</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.211792</v>
+        <v>-0.719784</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2.043642</v>
+        <v>-2.043642</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.075485</v>
+        <v>-3.075485</v>
       </c>
     </row>
     <row r="12">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2645,7 +2645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Funds received from option agreement 50,000</t>
+          <t>Funds received from option agreement                                         50,000</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Funds received from option agreement 50,000</t>
+          <t>Funds received from option agreement                                         50,000</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5460,7 +5460,11 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.507992</v>
       </c>
@@ -5560,10 +5564,10 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-2.043642</v>
+        <v>2.043642</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-3.075485</v>
+        <v>3.075485</v>
       </c>
     </row>
     <row r="97">
@@ -6070,6 +6074,204 @@
         </is>
       </c>
       <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>equity $                                                                                  29,325,545          1,514,500 (48,400) - 197,607 111,383 (12,213,651) 18,886,984           1,775,100 (6,994) (3,895,850) 16,759,240                              Total</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>$ (3,895,850) 37,488,007 Deficit (21,378,506)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>-33.592157</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>-12.213651</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares total</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>$                                                                         4,495,247                                  (58,546) 111,383          4,570,868                                       4,570,868                                                Reserves                                                                                                                                                                                                                                                                                                                                                                      financial</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>$                                                                         4,495,247                                  (58,546) 111,383          4,570,868                                       4,570,868                                                Reserves                                                                                                                                                                                                                                                                                                                                                                      financial to - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/BLLG.xlsx
+++ b/output/pdf_financials_xlsx/BLLG.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.570868</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.570868</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.377205</v>
       </c>
     </row>
     <row r="93">
@@ -3280,7 +3280,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3564,7 +3568,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>4.570868</v>
       </c>

--- a/output/pdf_financials_xlsx/BLLG.xlsx
+++ b/output/pdf_financials_xlsx/BLLG.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.719784</v>
+        <v>8.718851000000001</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2.043642</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.719784</v>
+        <v>-8.718851000000001</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-2.043642</v>
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.092475</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.029202</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.040402</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-12.213651</v>
+        <v>-12.306126</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.89585</v>
+        <v>-3.925052</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.424799</v>
+        <v>-3.465201</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-12.213651</v>
+        <v>-12.306126</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.89585</v>
+        <v>-3.925052</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.424799</v>
+        <v>-3.465201</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.056756</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.816615</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.410147</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.9555</v>
+        <v>2.012256</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.19575</v>
+        <v>1.012365</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.003375</v>
+        <v>1.413522</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.101267</v>
+        <v>0.044511</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.846101</v>
+        <v>0.029486</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.497484</v>
+        <v>1.087337</v>
       </c>
     </row>
     <row r="49">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -2920,7 +2920,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.649644</v>
       </c>
@@ -4860,7 +4864,11 @@
           <t>Renewal of reclamation deposit</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>-0.007</v>
       </c>
@@ -5625,7 +5633,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -5952,14 +5960,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>-8.718851000000001</v>
+        <v>8.718851000000001</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-2.043642</v>
+        <v>2.043642</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BLLG.xlsx
+++ b/output/pdf_financials_xlsx/BLLG.xlsx
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.049602</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.073445</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.200645</v>
       </c>
     </row>
     <row r="111">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.146555</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.025054</v>
       </c>
     </row>
     <row r="116">
@@ -3698,7 +3698,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4027,7 +4031,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4744,7 +4752,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.049602</v>
       </c>
@@ -4899,7 +4911,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.146555</v>
       </c>
